--- a/target/classes/Repository/OrangeHRM_Excel.xlsx
+++ b/target/classes/Repository/OrangeHRM_Excel.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
   <si>
     <t>User_Role</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>299196A</t>
+  </si>
+  <si>
+    <t>2985403A</t>
   </si>
 </sst>
 </file>
@@ -663,7 +666,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>8</v>

--- a/target/classes/Repository/OrangeHRM_Excel.xlsx
+++ b/target/classes/Repository/OrangeHRM_Excel.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="87">
   <si>
     <t>User_Role</t>
   </si>
